--- a/data_raw/MWM_dict.xlsx
+++ b/data_raw/MWM_dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\science\LongGold\development\tests\MWM\data_raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7603D27-DF26-49F2-8E12-2C593093926A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C10C3A-9EF0-49E4-92AA-4F077BA6031F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,9 +79,6 @@
     <t>VALUE</t>
   </si>
   <si>
-    <t>Du wirst zwei Melodien hintereinander hören, die sich in dem emotionalen Ausdruck unterscheiden, mit dem sie gespielt wurden.   Deine Aufgabe ist es, diejenige Melodie auszuwählen, die deiner Meinung nach, dem emotionalen Ausdruck in der Fragestellung am nächsten kommt. \\  Bitte höre dir beide Melodien immer ganz an, bevor du deine Antwort auswählst. Fallst du dir nicht sicher bist, wähle einfach deine beste Vermutung aus.  Antworten können sich wiederholen, und Du kannst mehrmals hintereinander dieselbe Antwortmöglichkeit wählen.</t>
-  </si>
-  <si>
     <t>Frage {{num_question}} von {{test_length}}</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
   </si>
   <si>
     <t>Werte</t>
-  </si>
-  <si>
-    <t>You will now hear two different versions of a melody at a time; these will differ in terms of the emotions expressed between performances. Your task is to judge the emotional expression of each version by selecting which of the two melodies you believe to be most representative of the emotion in question. \\ Questions may be repeated, so do not worry about making the same selection twice. Please listen to each sound clip in full before making your decision. If you don’t know the answer, give your best guess.</t>
   </si>
   <si>
     <t>Question {{num_question}} out of {{test_length}}</t>
@@ -212,24 +206,9 @@
     <t>In diesem Beispiel wollte der Musiker einen fröhlichen Ausdruck in der Melodie vermitteln, die vor dem Piepton zu hören war, und einen traurigen Ausdruck in der Melodie, die nach dem Piepton zu hören war. Die richtige Antwort wäre also Nummer 1. Du kannst gerne noch einmal zuhören, bevor du fortfährst.</t>
   </si>
   <si>
-    <t>For each trial, the two melodies you hear will be identical except that they will each be intended to communicate a different expression. Listen to the following clip by clicking the play button, and decide which of the two melodies sounds **happier** to you.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Here, the performer intended to convey a happy expression in the melody heard before the beep, and a sad expression in the melody heard after the beep, so the correct answer would have been clip 1. Feel free to listen again before moving on.</t>
-  </si>
-  <si>
-    <t>&lt;h4&gt;Willkommen zur Emotionen-Unterscheidungstest Übung&lt;/h4&gt;  Du wirst gleich gebeten dir zwei aufgezeichnete Melodiepaare anzuhören, die mit der Absicht aufgenommen wurden, eine von fünf bestimmten Emotionen auszudrücken: Wut, Angst, Freude, Trauer und Zärtlichkeit. Deine Aufgabe ist es die Aufnahme zu benennen, die die gesuchte Emotion zeigt. \\ Zuerst wirst du Beispiele hören und dann ein paar Übungsaufgaben machen.</t>
-  </si>
-  <si>
-    <t>&lt;h4&gt;Welcome to the Musical Emotion Discrimination Training&lt;/h4&gt;  You will be asked to listen to pairs of pre-recorded melodies which were performed with the intention of expressing one of five emotional categories: anger, fear, happiness, sadness or tenderness. Your task is to discriminate between the expressions communicated in each clip. \\ First, you’ll hear some examples and do a few practice questions.</t>
-  </si>
-  <si>
     <t>**Übungsfrage 1** \\ Bitte höre dir die folgenden Clips an und wähle aus, welcher für dich **wütender** klingt. \\ Wähle 1 für den Clip, der vor dem Piepton zu hören ist, oder 2 für den Clip, der nach dem Piepton zu hören ist.</t>
   </si>
   <si>
-    <t xml:space="preserve">**Practice question 1** \\ Please listen to the following clips and select which one sounds **angrier** to you. \\  Select 1 for the clip heard before the beep, or 2 for the clip heard after the beep. </t>
-  </si>
-  <si>
     <t xml:space="preserve">**{{feedback}}** \\ **Übungsfrage 2** \\ Bitte höre dir die folgenden Clips an und wähle aus, welcher für dich **trauriger** klingt. \\ Wähle 1 für den Clip, der vor dem Piepton zu hören ist, oder 2 für den Clip, der nach dem Piepton zu hören ist. </t>
   </si>
   <si>
@@ -239,9 +218,6 @@
     <t>DE_F</t>
   </si>
   <si>
-    <t>Sie werden zwei Melodien hintereinander hören, die sich in dem emotionalen Ausdruck unterscheiden, mit dem sie gespielt wurden.   Ihre Aufgabe ist es, diejenige Melodie auszuwählen, die Ihrer Meinung nach, dem emotionalen Ausdruck in der Fragestellung am nächsten kommt. \\  Bitte hören Sie sich beide Melodien immer ganz an, bevor Sie Ihre Antwort auswählen. Fallst Sie sich nicht sicher sind, wählen Sie einfach Ihre beste Vermutung aus.  Antworten können sich wiederholen, und Sie können mehrmals hintereinander dieselbe Antwortmöglichkeit wählen.</t>
-  </si>
-  <si>
     <t>Der Browser unterstützt kein Audio. Dieser Test funktioniert nicht ohne Audio, sorry!</t>
   </si>
   <si>
@@ -260,19 +236,6 @@
     <t>Ihr Testergebnis</t>
   </si>
   <si>
-    <t>&lt;h4&gt;Willkommen zur Emotionen-Unterscheidungstest Übung&lt;/h4&gt;  Sie werden gleich gebeten, sich zwei aufgezeichnete Melodiepaare anzuhören, die mit der Absicht aufgenommen wurden, eine von fünf bestimmten Emotionen auszudrücken: Wut, Angst, Freude, Trauer und Zärtlichkeit. Ihre Aufgabe ist es, diejenige Aufnahme zu benennen, die die gesuchte Emotion zeigt. \\ Zuerst werden Sie Beispiele hören und dann ein paar Übungsaufgaben machen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bei jedem Durchgang sind die beiden Melodien, die Sie hören, musikalisch identisch, aber sie sollen jeweils einen anderen Ausdruck vermitteln. Hör Sie sich den folgenden Clip an, indem Sie auf die Wiedergabetaste klicken, und entscheiden Sie, welche der beiden Melodien für Sie **fröhlicher** klingt.
-</t>
-  </si>
-  <si>
-    <t>In diesem Beispiel wollte der Musiker einen fröhlichen Ausdruck in der Melodie vermitteln, die vor dem Piepton zu hören war, und einen traurigen Ausdruck in der Melodie, die nach dem Piepton zu hören war. Die richtige Antwort wäre also Nummer 1. Sie können gerne noch einmal zuhören, bevor Sie fortfahren.</t>
-  </si>
-  <si>
-    <t>**Übungsfrage 1** \\ Bitte höre Sie sich die folgenden Clips an und wählen Sie aus, welcher für Sie **wütender** klingt. \\ Wählen Sie 1 für den Clip, der vor dem Piepton zu hören ist, oder 2 für den Clip, der nach dem Piepton zu hören ist.</t>
-  </si>
-  <si>
     <t xml:space="preserve">**{{feedback}}** \\ **Übungsfrage 2** \\ Bitte hören Sie sich die folgenden Clips an und wähle Sie aus, welcher für Sie **trauriger** klingt. \\ Wählen Sie 1 für den Clip, der vor dem Piepton zu hören ist, oder 2 für den Clip, der nach dem Piepton zu hören ist. </t>
   </si>
   <si>
@@ -315,9 +278,6 @@
     <t>Verschieden</t>
   </si>
   <si>
-    <t>Differen t</t>
-  </si>
-  <si>
     <t>Du hast **{{accuracy}} %** der Aufgaben richtig erkannt.</t>
   </si>
   <si>
@@ -343,6 +303,46 @@
   </si>
   <si>
     <t>Please listen to the following clips and select whether the melodies were the **same** or **different**.</t>
+  </si>
+  <si>
+    <t>Different</t>
+  </si>
+  <si>
+    <t>Du wirst zwei Melodien hintereinander hören, durch eine kurfze Pause getrennt.  Deine Aufgabe ist es zu beurteilen, ob die Melodien gleich oder verschieden sind.\\  Fallst du dir nicht sicher bist, wähle einfach deine beste Vermutung aus.  Antworten können sich wiederholen, und Du kannst mehrmals hintereinander dieselbe Antwortmöglichkeit wählen.</t>
+  </si>
+  <si>
+    <t>Sie werden zwei Melodien hintereinander hören, durch eine kurze Pause getrennt. Ihre Aufgabe ist es zu beurteilen, ob die Melodien gleich oder verschieden sind.\\  Falls Sie sich nicht sicher sind, wählen Sie einfach Ihre beste Vermutung aus.  Antworten können sich wiederholen, und Sie können mehrmals hintereinander dieselbe Antwortmöglichkeit wählen.</t>
+  </si>
+  <si>
+    <t>You will hear two melodies in succession, separated by a short pause. Your task is to determine whether the melodies are the same or different.\\  If you are unsure, just choose your best guess.  Answers may repeat, and you may select the same answer option several times in a row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DuSie werden gleich gebeten, sich  Melodiepaare anzuhören. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ihre Aufgabe ist es, zu beurteilen, ob die Melodien gleich oder verschieden waren. \\ </t>
+  </si>
+  <si>
+    <t>Zuerst werden Sie Beispiele hören und dann ein paar Übungsaufgaben machen.</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Willkommen zum Musikgedächtnistest&lt;/h4&gt;  
+DuSie werden gleich gebeten, sich  Melodiepaare anzuhören. Ihre Aufgabe ist es, zu beurteilen, ob die Melodien gleich oder verschieden waren. \\ Zuerst werden Sie Beispiele hören und dann ein paar Übungsaufgaben machen.</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Willkommen zum Musikgedächtnistest&lt;/h4&gt;  Du wirst gleich gebeten dir Melodiepaare anzuhören. Deine Aufgabe ist es zu beurteilen, ob die Melodien gleich oder verschieden waren. \\ Zuerst wirst du Beispiele hören und dann ein paar Übungsaufgaben machen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You will soon be asked to listen to pairs of melodies. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your task is to determine whether the melodies were the same or different. \\ </t>
+  </si>
+  <si>
+    <t>First, you will hear some examples, and then you will complete a few practice exercises.</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Welcome to the Music Memory Test&lt;/h4&gt;  You will be asked to listen to pairs of melodies. Your task is to determine whether the melodies were the same or different. \\ First, you will hear some examples, and then you will complete a few practice exercises.</t>
   </si>
 </sst>
 </file>
@@ -778,7 +778,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -789,27 +789,27 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="270" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -817,13 +817,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -831,13 +831,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -845,13 +845,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -859,13 +859,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -873,13 +873,13 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -887,13 +887,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -901,13 +901,13 @@
         <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -915,13 +915,13 @@
         <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -929,13 +929,13 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -943,13 +943,13 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -957,13 +957,13 @@
         <v>15</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -971,13 +971,13 @@
         <v>16</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -985,13 +985,13 @@
         <v>17</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -999,181 +999,181 @@
         <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="2" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="225" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="B19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="135" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="135" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
